--- a/module_4_data_transformation/Data_Modelling.xlsx
+++ b/module_4_data_transformation/Data_Modelling.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\de\data_engineering_practices\module_4_data_transformation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{23BD072B-4869-4BBC-9177-FE3EC3A54907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89811DA5-C5AA-4D12-AEDD-32258FE1EE5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="500" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" state="hidden" r:id="rId1"/>
@@ -473,9 +473,6 @@
     <t>Dimension</t>
   </si>
   <si>
-    <t>dim_date</t>
-  </si>
-  <si>
     <t>dim_customer</t>
   </si>
   <si>
@@ -525,6 +522,9 @@
     <t>List of attributes</t>
   </si>
   <si>
+    <t>dim_calendar</t>
+  </si>
+  <si>
     <t>Table dim_date {
   date_key     integer [primary key]
   full_date    varchar [not null]
@@ -537,11 +537,11 @@
   is_weekend   boolean [not null]
 }
 Table dim_customer {
-  customer_unique_id varchar [primary key]
-  customer_id        varchar [not null]
-  customer_zip_code  varchar
-  customer_city      varchar
-  customer_state     varchar
+  id varchar [primary key]
+  customer_string        varchar [not null]
+  postcode  varchar
+  city      varchar
+  state     varchar
 }
 Table dim_order_status {
   order_status_id  integer [primary key]
@@ -984,66 +984,27 @@
     <xf numFmtId="0" fontId="24" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1077,31 +1038,70 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5362,442 +5362,442 @@
   <sheetData>
     <row r="1" spans="1:22" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="54" t="s">
+      <c r="A2" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="54"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="54"/>
-      <c r="N2" s="54"/>
-      <c r="O2" s="54"/>
-      <c r="P2" s="54"/>
-      <c r="Q2" s="54"/>
-      <c r="R2" s="54"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19"/>
+      <c r="O2" s="19"/>
+      <c r="P2" s="19"/>
+      <c r="Q2" s="19"/>
+      <c r="R2" s="19"/>
       <c r="V2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3" spans="1:22" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="V3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="55" t="s">
+      <c r="A4" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="56" t="s">
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="57" t="s">
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="58" t="s">
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="K4" s="58"/>
-      <c r="L4" s="58"/>
-      <c r="M4" s="59" t="s">
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="N4" s="59"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="60" t="s">
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
+      <c r="Q4" s="25"/>
+      <c r="R4" s="25"/>
     </row>
     <row r="5" spans="1:22" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="49" t="s">
+      <c r="A5" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="50" t="s">
+      <c r="B5" s="32"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="51" t="s">
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
-      <c r="J5" s="52" t="s">
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="K5" s="52"/>
-      <c r="L5" s="52"/>
-      <c r="M5" s="53" t="s">
+      <c r="K5" s="35"/>
+      <c r="L5" s="35"/>
+      <c r="M5" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="N5" s="53"/>
-      <c r="O5" s="53"/>
-      <c r="P5" s="43" t="s">
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="Q5" s="43"/>
-      <c r="R5" s="43"/>
+      <c r="Q5" s="26"/>
+      <c r="R5" s="26"/>
     </row>
     <row r="6" spans="1:22" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="44"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="45" t="s">
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="44" t="s">
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="46" t="s">
+      <c r="H6" s="27"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="K6" s="46"/>
-      <c r="L6" s="46"/>
-      <c r="M6" s="47" t="s">
+      <c r="K6" s="29"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="N6" s="47"/>
-      <c r="O6" s="47"/>
-      <c r="P6" s="48" t="s">
+      <c r="N6" s="30"/>
+      <c r="O6" s="30"/>
+      <c r="P6" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="Q6" s="48"/>
-      <c r="R6" s="48"/>
+      <c r="Q6" s="31"/>
+      <c r="R6" s="31"/>
     </row>
     <row r="7" spans="1:22" ht="6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="38"/>
-      <c r="B7" s="38"/>
-      <c r="C7" s="38"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="40"/>
-      <c r="I7" s="40"/>
-      <c r="J7" s="41"/>
-      <c r="K7" s="41"/>
-      <c r="L7" s="41"/>
-      <c r="M7" s="42"/>
-      <c r="N7" s="42"/>
-      <c r="O7" s="42"/>
-      <c r="P7" s="33"/>
-      <c r="Q7" s="33"/>
-      <c r="R7" s="33"/>
+      <c r="A7" s="42"/>
+      <c r="B7" s="42"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="44"/>
+      <c r="I7" s="44"/>
+      <c r="J7" s="45"/>
+      <c r="K7" s="45"/>
+      <c r="L7" s="45"/>
+      <c r="M7" s="46"/>
+      <c r="N7" s="46"/>
+      <c r="O7" s="46"/>
+      <c r="P7" s="37"/>
+      <c r="Q7" s="37"/>
+      <c r="R7" s="37"/>
     </row>
     <row r="8" spans="1:22" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="79" spans="1:18" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="34" t="s">
+      <c r="A79" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="B79" s="34"/>
-      <c r="C79" s="34"/>
-      <c r="D79" s="34"/>
-      <c r="E79" s="34"/>
-      <c r="F79" s="34"/>
-      <c r="G79" s="34"/>
-      <c r="H79" s="34"/>
-      <c r="I79" s="34"/>
-      <c r="J79" s="34"/>
-      <c r="K79" s="34"/>
-      <c r="L79" s="34"/>
-      <c r="M79" s="34"/>
-      <c r="N79" s="34"/>
-      <c r="O79" s="34"/>
-      <c r="P79" s="34"/>
-      <c r="Q79" s="34"/>
-      <c r="R79" s="34"/>
+      <c r="B79" s="38"/>
+      <c r="C79" s="38"/>
+      <c r="D79" s="38"/>
+      <c r="E79" s="38"/>
+      <c r="F79" s="38"/>
+      <c r="G79" s="38"/>
+      <c r="H79" s="38"/>
+      <c r="I79" s="38"/>
+      <c r="J79" s="38"/>
+      <c r="K79" s="38"/>
+      <c r="L79" s="38"/>
+      <c r="M79" s="38"/>
+      <c r="N79" s="38"/>
+      <c r="O79" s="38"/>
+      <c r="P79" s="38"/>
+      <c r="Q79" s="38"/>
+      <c r="R79" s="38"/>
     </row>
     <row r="80" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="35" t="s">
+      <c r="A80" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="B80" s="35"/>
-      <c r="C80" s="35"/>
-      <c r="D80" s="35"/>
-      <c r="E80" s="35"/>
-      <c r="F80" s="35"/>
-      <c r="G80" s="35"/>
-      <c r="H80" s="35"/>
-      <c r="I80" s="35"/>
-      <c r="J80" s="35"/>
-      <c r="K80" s="35"/>
-      <c r="L80" s="35"/>
-      <c r="M80" s="35"/>
-      <c r="N80" s="35"/>
-      <c r="O80" s="35"/>
-      <c r="P80" s="35"/>
-      <c r="Q80" s="35"/>
-      <c r="R80" s="35"/>
+      <c r="B80" s="39"/>
+      <c r="C80" s="39"/>
+      <c r="D80" s="39"/>
+      <c r="E80" s="39"/>
+      <c r="F80" s="39"/>
+      <c r="G80" s="39"/>
+      <c r="H80" s="39"/>
+      <c r="I80" s="39"/>
+      <c r="J80" s="39"/>
+      <c r="K80" s="39"/>
+      <c r="L80" s="39"/>
+      <c r="M80" s="39"/>
+      <c r="N80" s="39"/>
+      <c r="O80" s="39"/>
+      <c r="P80" s="39"/>
+      <c r="Q80" s="39"/>
+      <c r="R80" s="39"/>
     </row>
     <row r="81" spans="1:18" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="36" t="s">
+      <c r="A81" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="B81" s="36"/>
-      <c r="C81" s="36"/>
-      <c r="D81" s="36"/>
-      <c r="E81" s="36"/>
-      <c r="F81" s="36"/>
-      <c r="G81" s="36"/>
-      <c r="H81" s="36"/>
-      <c r="I81" s="36"/>
-      <c r="J81" s="36"/>
-      <c r="K81" s="36"/>
-      <c r="L81" s="36"/>
-      <c r="M81" s="36"/>
-      <c r="N81" s="36"/>
-      <c r="O81" s="36"/>
-      <c r="P81" s="36"/>
-      <c r="Q81" s="36"/>
-      <c r="R81" s="36"/>
+      <c r="B81" s="40"/>
+      <c r="C81" s="40"/>
+      <c r="D81" s="40"/>
+      <c r="E81" s="40"/>
+      <c r="F81" s="40"/>
+      <c r="G81" s="40"/>
+      <c r="H81" s="40"/>
+      <c r="I81" s="40"/>
+      <c r="J81" s="40"/>
+      <c r="K81" s="40"/>
+      <c r="L81" s="40"/>
+      <c r="M81" s="40"/>
+      <c r="N81" s="40"/>
+      <c r="O81" s="40"/>
+      <c r="P81" s="40"/>
+      <c r="Q81" s="40"/>
+      <c r="R81" s="40"/>
     </row>
     <row r="82" spans="1:18" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="83" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="37" t="s">
+      <c r="A83" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="B83" s="37"/>
-      <c r="C83" s="37"/>
-      <c r="D83" s="37"/>
-      <c r="E83" s="37"/>
-      <c r="F83" s="37"/>
-      <c r="G83" s="37"/>
-      <c r="H83" s="37"/>
-      <c r="I83" s="37"/>
-      <c r="J83" s="37"/>
-      <c r="K83" s="37"/>
-      <c r="L83" s="37"/>
-      <c r="M83" s="37"/>
-      <c r="N83" s="37"/>
-      <c r="O83" s="37"/>
-      <c r="P83" s="37"/>
-      <c r="Q83" s="37"/>
-      <c r="R83" s="37"/>
+      <c r="B83" s="41"/>
+      <c r="C83" s="41"/>
+      <c r="D83" s="41"/>
+      <c r="E83" s="41"/>
+      <c r="F83" s="41"/>
+      <c r="G83" s="41"/>
+      <c r="H83" s="41"/>
+      <c r="I83" s="41"/>
+      <c r="J83" s="41"/>
+      <c r="K83" s="41"/>
+      <c r="L83" s="41"/>
+      <c r="M83" s="41"/>
+      <c r="N83" s="41"/>
+      <c r="O83" s="41"/>
+      <c r="P83" s="41"/>
+      <c r="Q83" s="41"/>
+      <c r="R83" s="41"/>
     </row>
     <row r="84" spans="1:18" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="28" t="s">
+      <c r="A84" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="B84" s="28"/>
-      <c r="C84" s="28"/>
-      <c r="D84" s="28"/>
-      <c r="E84" s="28"/>
-      <c r="F84" s="28"/>
-      <c r="G84" s="28"/>
-      <c r="H84" s="28"/>
-      <c r="I84" s="28"/>
-      <c r="J84" s="28"/>
-      <c r="K84" s="28"/>
-      <c r="L84" s="28"/>
-      <c r="M84" s="28"/>
-      <c r="N84" s="28"/>
-      <c r="O84" s="28"/>
-      <c r="P84" s="28"/>
-      <c r="Q84" s="28"/>
-      <c r="R84" s="28"/>
+      <c r="B84" s="51"/>
+      <c r="C84" s="51"/>
+      <c r="D84" s="51"/>
+      <c r="E84" s="51"/>
+      <c r="F84" s="51"/>
+      <c r="G84" s="51"/>
+      <c r="H84" s="51"/>
+      <c r="I84" s="51"/>
+      <c r="J84" s="51"/>
+      <c r="K84" s="51"/>
+      <c r="L84" s="51"/>
+      <c r="M84" s="51"/>
+      <c r="N84" s="51"/>
+      <c r="O84" s="51"/>
+      <c r="P84" s="51"/>
+      <c r="Q84" s="51"/>
+      <c r="R84" s="51"/>
     </row>
     <row r="85" spans="1:18" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="86" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="29" t="s">
+      <c r="A86" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="B86" s="29"/>
-      <c r="C86" s="29"/>
-      <c r="D86" s="29"/>
-      <c r="E86" s="29"/>
-      <c r="F86" s="29"/>
-      <c r="G86" s="29"/>
-      <c r="H86" s="29"/>
-      <c r="I86" s="29"/>
-      <c r="J86" s="29"/>
-      <c r="K86" s="29"/>
-      <c r="L86" s="29"/>
-      <c r="M86" s="29"/>
-      <c r="N86" s="29"/>
-      <c r="O86" s="29"/>
-      <c r="P86" s="29"/>
-      <c r="Q86" s="29"/>
-      <c r="R86" s="29"/>
+      <c r="B86" s="52"/>
+      <c r="C86" s="52"/>
+      <c r="D86" s="52"/>
+      <c r="E86" s="52"/>
+      <c r="F86" s="52"/>
+      <c r="G86" s="52"/>
+      <c r="H86" s="52"/>
+      <c r="I86" s="52"/>
+      <c r="J86" s="52"/>
+      <c r="K86" s="52"/>
+      <c r="L86" s="52"/>
+      <c r="M86" s="52"/>
+      <c r="N86" s="52"/>
+      <c r="O86" s="52"/>
+      <c r="P86" s="52"/>
+      <c r="Q86" s="52"/>
+      <c r="R86" s="52"/>
     </row>
     <row r="87" spans="1:18" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="30" t="s">
+      <c r="A87" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="B87" s="30"/>
-      <c r="C87" s="30"/>
-      <c r="D87" s="30"/>
-      <c r="E87" s="30"/>
-      <c r="F87" s="30"/>
-      <c r="G87" s="30"/>
-      <c r="H87" s="30"/>
-      <c r="I87" s="30"/>
-      <c r="J87" s="30"/>
-      <c r="K87" s="30"/>
-      <c r="L87" s="30"/>
-      <c r="M87" s="30"/>
-      <c r="N87" s="30"/>
-      <c r="O87" s="30"/>
-      <c r="P87" s="30"/>
-      <c r="Q87" s="30"/>
-      <c r="R87" s="30"/>
+      <c r="B87" s="53"/>
+      <c r="C87" s="53"/>
+      <c r="D87" s="53"/>
+      <c r="E87" s="53"/>
+      <c r="F87" s="53"/>
+      <c r="G87" s="53"/>
+      <c r="H87" s="53"/>
+      <c r="I87" s="53"/>
+      <c r="J87" s="53"/>
+      <c r="K87" s="53"/>
+      <c r="L87" s="53"/>
+      <c r="M87" s="53"/>
+      <c r="N87" s="53"/>
+      <c r="O87" s="53"/>
+      <c r="P87" s="53"/>
+      <c r="Q87" s="53"/>
+      <c r="R87" s="53"/>
     </row>
     <row r="88" spans="1:18" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="89" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="31" t="s">
+      <c r="A89" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="B89" s="31"/>
-      <c r="C89" s="31"/>
-      <c r="D89" s="31"/>
-      <c r="E89" s="31"/>
-      <c r="F89" s="31"/>
-      <c r="G89" s="31"/>
-      <c r="H89" s="31"/>
-      <c r="I89" s="31"/>
-      <c r="J89" s="31"/>
-      <c r="K89" s="31"/>
-      <c r="L89" s="31"/>
-      <c r="M89" s="31"/>
-      <c r="N89" s="31"/>
-      <c r="O89" s="31"/>
-      <c r="P89" s="31"/>
-      <c r="Q89" s="31"/>
-      <c r="R89" s="31"/>
+      <c r="B89" s="54"/>
+      <c r="C89" s="54"/>
+      <c r="D89" s="54"/>
+      <c r="E89" s="54"/>
+      <c r="F89" s="54"/>
+      <c r="G89" s="54"/>
+      <c r="H89" s="54"/>
+      <c r="I89" s="54"/>
+      <c r="J89" s="54"/>
+      <c r="K89" s="54"/>
+      <c r="L89" s="54"/>
+      <c r="M89" s="54"/>
+      <c r="N89" s="54"/>
+      <c r="O89" s="54"/>
+      <c r="P89" s="54"/>
+      <c r="Q89" s="54"/>
+      <c r="R89" s="54"/>
     </row>
     <row r="90" spans="1:18" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="32" t="s">
+      <c r="A90" s="55" t="s">
         <v>27</v>
       </c>
-      <c r="B90" s="32"/>
-      <c r="C90" s="32"/>
-      <c r="D90" s="32"/>
-      <c r="E90" s="32"/>
-      <c r="F90" s="32"/>
-      <c r="G90" s="32"/>
-      <c r="H90" s="32"/>
-      <c r="I90" s="32"/>
-      <c r="J90" s="32"/>
-      <c r="K90" s="32"/>
-      <c r="L90" s="32"/>
-      <c r="M90" s="32"/>
-      <c r="N90" s="32"/>
-      <c r="O90" s="32"/>
-      <c r="P90" s="32"/>
-      <c r="Q90" s="32"/>
-      <c r="R90" s="32"/>
+      <c r="B90" s="55"/>
+      <c r="C90" s="55"/>
+      <c r="D90" s="55"/>
+      <c r="E90" s="55"/>
+      <c r="F90" s="55"/>
+      <c r="G90" s="55"/>
+      <c r="H90" s="55"/>
+      <c r="I90" s="55"/>
+      <c r="J90" s="55"/>
+      <c r="K90" s="55"/>
+      <c r="L90" s="55"/>
+      <c r="M90" s="55"/>
+      <c r="N90" s="55"/>
+      <c r="O90" s="55"/>
+      <c r="P90" s="55"/>
+      <c r="Q90" s="55"/>
+      <c r="R90" s="55"/>
     </row>
     <row r="91" spans="1:18" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="92" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="24" t="s">
+      <c r="A92" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="B92" s="24"/>
-      <c r="C92" s="24"/>
-      <c r="D92" s="24"/>
-      <c r="E92" s="24"/>
-      <c r="F92" s="24"/>
-      <c r="G92" s="24"/>
-      <c r="H92" s="24"/>
-      <c r="I92" s="24"/>
-      <c r="J92" s="24"/>
-      <c r="K92" s="24"/>
-      <c r="L92" s="24"/>
-      <c r="M92" s="24"/>
-      <c r="N92" s="24"/>
-      <c r="O92" s="24"/>
-      <c r="P92" s="24"/>
-      <c r="Q92" s="24"/>
-      <c r="R92" s="24"/>
+      <c r="B92" s="47"/>
+      <c r="C92" s="47"/>
+      <c r="D92" s="47"/>
+      <c r="E92" s="47"/>
+      <c r="F92" s="47"/>
+      <c r="G92" s="47"/>
+      <c r="H92" s="47"/>
+      <c r="I92" s="47"/>
+      <c r="J92" s="47"/>
+      <c r="K92" s="47"/>
+      <c r="L92" s="47"/>
+      <c r="M92" s="47"/>
+      <c r="N92" s="47"/>
+      <c r="O92" s="47"/>
+      <c r="P92" s="47"/>
+      <c r="Q92" s="47"/>
+      <c r="R92" s="47"/>
     </row>
     <row r="93" spans="1:18" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="25" t="s">
+      <c r="A93" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="B93" s="25"/>
-      <c r="C93" s="25"/>
-      <c r="D93" s="25"/>
-      <c r="E93" s="25"/>
-      <c r="F93" s="25"/>
-      <c r="G93" s="25"/>
-      <c r="H93" s="25"/>
-      <c r="I93" s="25"/>
-      <c r="J93" s="25"/>
-      <c r="K93" s="25"/>
-      <c r="L93" s="25"/>
-      <c r="M93" s="25"/>
-      <c r="N93" s="25"/>
-      <c r="O93" s="25"/>
-      <c r="P93" s="25"/>
-      <c r="Q93" s="25"/>
-      <c r="R93" s="25"/>
+      <c r="B93" s="48"/>
+      <c r="C93" s="48"/>
+      <c r="D93" s="48"/>
+      <c r="E93" s="48"/>
+      <c r="F93" s="48"/>
+      <c r="G93" s="48"/>
+      <c r="H93" s="48"/>
+      <c r="I93" s="48"/>
+      <c r="J93" s="48"/>
+      <c r="K93" s="48"/>
+      <c r="L93" s="48"/>
+      <c r="M93" s="48"/>
+      <c r="N93" s="48"/>
+      <c r="O93" s="48"/>
+      <c r="P93" s="48"/>
+      <c r="Q93" s="48"/>
+      <c r="R93" s="48"/>
     </row>
     <row r="94" spans="1:18" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="95" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="26" t="s">
+      <c r="A95" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="B95" s="26"/>
-      <c r="C95" s="26"/>
-      <c r="D95" s="26"/>
-      <c r="E95" s="26"/>
-      <c r="F95" s="26"/>
-      <c r="G95" s="26"/>
-      <c r="H95" s="26"/>
-      <c r="I95" s="26"/>
-      <c r="J95" s="26"/>
-      <c r="K95" s="26"/>
-      <c r="L95" s="26"/>
-      <c r="M95" s="26"/>
-      <c r="N95" s="26"/>
-      <c r="O95" s="26"/>
-      <c r="P95" s="26"/>
-      <c r="Q95" s="26"/>
-      <c r="R95" s="26"/>
+      <c r="B95" s="49"/>
+      <c r="C95" s="49"/>
+      <c r="D95" s="49"/>
+      <c r="E95" s="49"/>
+      <c r="F95" s="49"/>
+      <c r="G95" s="49"/>
+      <c r="H95" s="49"/>
+      <c r="I95" s="49"/>
+      <c r="J95" s="49"/>
+      <c r="K95" s="49"/>
+      <c r="L95" s="49"/>
+      <c r="M95" s="49"/>
+      <c r="N95" s="49"/>
+      <c r="O95" s="49"/>
+      <c r="P95" s="49"/>
+      <c r="Q95" s="49"/>
+      <c r="R95" s="49"/>
     </row>
     <row r="96" spans="1:18" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="27" t="s">
+      <c r="A96" s="50" t="s">
         <v>31</v>
       </c>
-      <c r="B96" s="27"/>
-      <c r="C96" s="27"/>
-      <c r="D96" s="27"/>
-      <c r="E96" s="27"/>
-      <c r="F96" s="27"/>
-      <c r="G96" s="27"/>
-      <c r="H96" s="27"/>
-      <c r="I96" s="27"/>
-      <c r="J96" s="27"/>
-      <c r="K96" s="27"/>
-      <c r="L96" s="27"/>
-      <c r="M96" s="27"/>
-      <c r="N96" s="27"/>
-      <c r="O96" s="27"/>
-      <c r="P96" s="27"/>
-      <c r="Q96" s="27"/>
-      <c r="R96" s="27"/>
+      <c r="B96" s="50"/>
+      <c r="C96" s="50"/>
+      <c r="D96" s="50"/>
+      <c r="E96" s="50"/>
+      <c r="F96" s="50"/>
+      <c r="G96" s="50"/>
+      <c r="H96" s="50"/>
+      <c r="I96" s="50"/>
+      <c r="J96" s="50"/>
+      <c r="K96" s="50"/>
+      <c r="L96" s="50"/>
+      <c r="M96" s="50"/>
+      <c r="N96" s="50"/>
+      <c r="O96" s="50"/>
+      <c r="P96" s="50"/>
+      <c r="Q96" s="50"/>
+      <c r="R96" s="50"/>
     </row>
     <row r="97" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="130" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6281,13 +6281,25 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="A2:R2"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="M4:O4"/>
-    <mergeCell ref="P4:R4"/>
+    <mergeCell ref="A92:R92"/>
+    <mergeCell ref="A93:R93"/>
+    <mergeCell ref="A95:R95"/>
+    <mergeCell ref="A96:R96"/>
+    <mergeCell ref="A84:R84"/>
+    <mergeCell ref="A86:R86"/>
+    <mergeCell ref="A87:R87"/>
+    <mergeCell ref="A89:R89"/>
+    <mergeCell ref="A90:R90"/>
+    <mergeCell ref="P7:R7"/>
+    <mergeCell ref="A79:R79"/>
+    <mergeCell ref="A80:R80"/>
+    <mergeCell ref="A81:R81"/>
+    <mergeCell ref="A83:R83"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="M7:O7"/>
     <mergeCell ref="P5:R5"/>
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="D6:F6"/>
@@ -6300,25 +6312,13 @@
     <mergeCell ref="G5:I5"/>
     <mergeCell ref="J5:L5"/>
     <mergeCell ref="M5:O5"/>
-    <mergeCell ref="P7:R7"/>
-    <mergeCell ref="A79:R79"/>
-    <mergeCell ref="A80:R80"/>
-    <mergeCell ref="A81:R81"/>
-    <mergeCell ref="A83:R83"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="M7:O7"/>
-    <mergeCell ref="A92:R92"/>
-    <mergeCell ref="A93:R93"/>
-    <mergeCell ref="A95:R95"/>
-    <mergeCell ref="A96:R96"/>
-    <mergeCell ref="A84:R84"/>
-    <mergeCell ref="A86:R86"/>
-    <mergeCell ref="A87:R87"/>
-    <mergeCell ref="A89:R89"/>
-    <mergeCell ref="A90:R90"/>
+    <mergeCell ref="A2:R2"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="M4:O4"/>
+    <mergeCell ref="P4:R4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -6339,21 +6339,21 @@
       <c r="A1" s="1"/>
     </row>
     <row r="2" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="56" t="s">
         <v>88</v>
       </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
     </row>
     <row r="3" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
     </row>
     <row r="4" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="61" t="s">
+      <c r="A4" s="57" t="s">
         <v>89</v>
       </c>
-      <c r="B4" s="61"/>
-      <c r="C4" s="61"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
     </row>
     <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2"/>
@@ -6394,11 +6394,11 @@
       <c r="A10" s="1"/>
     </row>
     <row r="11" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="61" t="s">
+      <c r="A11" s="57" t="s">
         <v>95</v>
       </c>
-      <c r="B11" s="61"/>
-      <c r="C11" s="61"/>
+      <c r="B11" s="57"/>
+      <c r="C11" s="57"/>
     </row>
     <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2"/>
@@ -6439,11 +6439,11 @@
       <c r="A17" s="1"/>
     </row>
     <row r="18" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="61" t="s">
+      <c r="A18" s="57" t="s">
         <v>101</v>
       </c>
-      <c r="B18" s="61"/>
-      <c r="C18" s="61"/>
+      <c r="B18" s="57"/>
+      <c r="C18" s="57"/>
     </row>
     <row r="19" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2"/>
@@ -6498,11 +6498,11 @@
       <c r="A26" s="1"/>
     </row>
     <row r="27" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="61" t="s">
+      <c r="A27" s="57" t="s">
         <v>109</v>
       </c>
-      <c r="B27" s="61"/>
-      <c r="C27" s="61"/>
+      <c r="B27" s="57"/>
+      <c r="C27" s="57"/>
     </row>
     <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2"/>
@@ -6543,11 +6543,11 @@
       <c r="A33" s="1"/>
     </row>
     <row r="34" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="61" t="s">
+      <c r="A34" s="57" t="s">
         <v>114</v>
       </c>
-      <c r="B34" s="61"/>
-      <c r="C34" s="61"/>
+      <c r="B34" s="57"/>
+      <c r="C34" s="57"/>
     </row>
     <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="2"/>
@@ -6602,11 +6602,11 @@
       <c r="A42" s="1"/>
     </row>
     <row r="43" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="61" t="s">
+      <c r="A43" s="57" t="s">
         <v>121</v>
       </c>
-      <c r="B43" s="61"/>
-      <c r="C43" s="61"/>
+      <c r="B43" s="57"/>
+      <c r="C43" s="57"/>
     </row>
     <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="2"/>
@@ -6668,11 +6668,11 @@
       <c r="A52" s="1"/>
     </row>
     <row r="53" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="61" t="s">
+      <c r="A53" s="57" t="s">
         <v>128</v>
       </c>
-      <c r="B53" s="61"/>
-      <c r="C53" s="61"/>
+      <c r="B53" s="57"/>
+      <c r="C53" s="57"/>
     </row>
     <row r="54" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="2"/>
@@ -6741,11 +6741,11 @@
       <c r="A63" s="1"/>
     </row>
     <row r="64" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="61" t="s">
+      <c r="A64" s="57" t="s">
         <v>137</v>
       </c>
-      <c r="B64" s="61"/>
-      <c r="C64" s="61"/>
+      <c r="B64" s="57"/>
+      <c r="C64" s="57"/>
     </row>
     <row r="65" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="2"/>
@@ -6779,11 +6779,11 @@
       <c r="A69" s="1"/>
     </row>
     <row r="70" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="61" t="s">
+      <c r="A70" s="57" t="s">
         <v>141</v>
       </c>
-      <c r="B70" s="61"/>
-      <c r="C70" s="61"/>
+      <c r="B70" s="57"/>
+      <c r="C70" s="57"/>
     </row>
     <row r="71" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="3"/>
@@ -6801,16 +6801,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A70:C70"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A70:C70"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -6840,12 +6840,12 @@
       <c r="D2" s="1"/>
     </row>
     <row r="3" spans="1:4" ht="69.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="22" t="s">
-        <v>160</v>
-      </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
+      <c r="A3" s="61" t="s">
+        <v>159</v>
+      </c>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
     </row>
     <row r="4" spans="1:4" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
@@ -6854,12 +6854,12 @@
       <c r="D4" s="1"/>
     </row>
     <row r="5" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="59" t="s">
         <v>143</v>
       </c>
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
@@ -6886,13 +6886,13 @@
         <v>146</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.35">
@@ -6902,20 +6902,20 @@
       <c r="D9" s="1"/>
     </row>
     <row r="10" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="58" t="s">
+        <v>155</v>
+      </c>
+      <c r="B10" s="59"/>
+      <c r="C10" s="59"/>
+      <c r="D10" s="59"/>
+    </row>
+    <row r="11" spans="1:4" s="10" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="60" t="s">
         <v>156</v>
       </c>
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-    </row>
-    <row r="11" spans="1:4" s="10" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
+      <c r="B11" s="60"/>
+      <c r="C11" s="60"/>
+      <c r="D11" s="60"/>
     </row>
     <row r="12" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1"/>
@@ -6924,26 +6924,26 @@
       <c r="D12" s="1"/>
     </row>
     <row r="13" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="59" t="s">
         <v>147</v>
       </c>
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
+      <c r="B13" s="59"/>
+      <c r="C13" s="59"/>
+      <c r="D13" s="59"/>
     </row>
     <row r="14" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="15" t="s">
         <v>148</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
     </row>
     <row r="15" spans="1:4" s="10" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="16" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="B15" s="12"/>
       <c r="C15" s="12"/>
@@ -6951,23 +6951,23 @@
     </row>
     <row r="16" spans="1:4" s="10" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="17" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
       <c r="D16" s="13"/>
     </row>
     <row r="19" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="20" t="s">
-        <v>151</v>
-      </c>
-      <c r="B19" s="20"/>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
+      <c r="A19" s="59" t="s">
+        <v>150</v>
+      </c>
+      <c r="B19" s="59"/>
+      <c r="C19" s="59"/>
+      <c r="D19" s="59"/>
     </row>
     <row r="20" spans="1:4" s="10" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
@@ -6975,7 +6975,7 @@
     </row>
     <row r="21" spans="1:4" s="10" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B21" s="13"/>
       <c r="C21" s="13"/>
@@ -6983,7 +6983,7 @@
     </row>
     <row r="22" spans="1:4" s="10" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B22" s="13"/>
       <c r="C22" s="13"/>
